--- a/data/inputs/turnos_bloqueados.xlsx
+++ b/data/inputs/turnos_bloqueados.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/vacanze_romane/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D0DBE7-A0CB-1546-B3BC-A9E867253269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482EAC57-7BFC-2846-970D-2BC31E6666FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1660" windowWidth="27240" windowHeight="16160" xr2:uid="{FC2C9828-5E8A-BB4C-B788-AB4DEDCA70F7}"/>
   </bookViews>
@@ -475,7 +475,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="D2" s="1">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
